--- a/ig/main/CodeSystem-tre-r406-forme-activite-smsse-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r406-forme-activite-smsse-regulee.xlsx
@@ -163,6 +163,48 @@
     <t>Date de fin d'exploitation d'un code concept</t>
   </si>
   <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>rass</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le RASS</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
     <t>cisis</t>
   </si>
   <si>
@@ -170,48 +212,6 @@
   </si>
   <si>
     <t>Permet de définir les codes concepts uilisés par le CISIS</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>rass</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le RASS</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
   </si>
   <si>
     <t>Level</t>
@@ -840,21 +840,21 @@
         <v>51</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="C6" t="s" s="2">
+      <c r="D6" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -896,7 +896,7 @@
         <v>65</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
